--- a/SLR/Full-Paper-Read/Paper-Review/PS04.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS04.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
   <si>
     <t>ID</t>
   </si>
@@ -26,72 +26,70 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <t>The authors address the integration of technological advancements from dynamic adaptive systems and IT ecosystems into current software systems, particularly focusing on cyber-physical systems (CPS) for smart applications in various environments. However, they note that methodical engineering of cyber-physical ecosystems (CPES) remains a significant challenge. Traditional engineering methods do not adequately address the openness, uncertainty, and emergent properties of these ecosystems, which blur system boundaries at design time. The paper emphasizes the need for new engineering techniques for CPES, especially for aspects like time synchronization, execution control, and interaction structure. The authors highlight the potential of self-balanced control in CPES, which promises new applications but also demands new approaches in the engineering process, including requirements engineering and runtime verification. They review and summarize the challenges of applying control theory to CPES engineering. In essence, the paper presents a new perspective on CPS, predicting they will become more open and complex. It calls for the adoption of self-balanced control mechanisms in CPES and discusses the current state of the art in CPS and CSE, considering how these advancements can address the identified challenges in CPES.</t>
-  </si>
-  <si>
-    <t>the authors defined CPES (Cyber-Physical Ecosystems) as a combination of Software Ecosystems with CPS. They said: "In CPES we integrate the openness and adaptivity of software ecosystems with the modular and intelligent component coupling of CPS. Thereby new, combined research areas arise." 
-Research areas from the combination of the challenges in SECO and CPS: 
-A) the overall approach and evolution of the system: 1) evolution over time (adaptability) 2) self-learning composition (Intelligence and automation)
-B) the design time development approach: 1) Open and Closed World Modelling Approach (Model and Model-Driven Engineering) 2) Interdisciplinary Modelling Approach (Interoperability and Adaptability)
-C) the operation approach during runtime of the system: 1) Openness Based Uncertainty in Adaptation (Adaptability) 2) Controlled Adaption of Functionality w.r.t. Dependability
-2nd Reviewer: This paper also mentiones unceartainty as a main concept of CPES (similar to PS03)</t>
+    <t>The study aims to catalouge through a mapping study the practices of automotive software engineering, motivated by the change from hardware to software centric development. 679 articles are analysed. RQ1: What is the intensity of research on automotive software engineering? RQ2: What are the msot frequenctly invistaegated research topics? RQ3: What are the most frequently applied research types? RQ4: What kind of contributions are provided by studies? RQ5: What are the research gaps? Following research themes and challenges: Theme 1. Comprehensive automotive architectureTheme 2. Reducing complexity
+• Theme 3. Improving development processes
+• Theme 4. Seamless model-driven development
+• Theme 5. Integrated tool support
+• Theme 6. Learning from other domains
+• Theme 7. Improving quality and reliability
+• Theme 8. Standardized automotive software and system infras_x0002_tructure
+The paper answers the RQs and provide nuanced commentary on all of the topics.</t>
+  </si>
+  <si>
+    <t>The mapping study is not directly linked with out study, but there are some interesting outputs as it is linked with software engineering. However, most of the data points in the review protocol are not relevant for this study.</t>
   </si>
   <si>
     <t>CPS Case Study / Example availability</t>
   </si>
   <si>
+    <t>&lt;add your comment here if any&gt;</t>
+  </si>
+  <si>
+    <t>SECO Tools Availability (add repository or website in the comment)</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
+  </si>
+  <si>
+    <t>Modeling and Model-Driven Engineering</t>
+  </si>
+  <si>
+    <t>Continuous software and system engineering</t>
+  </si>
+  <si>
     <t>n.a.</t>
   </si>
   <si>
-    <t>&lt;add your comment here if any&gt;</t>
-  </si>
-  <si>
-    <t>SECO Tools Availability (add repository or website in the comment)</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
-  </si>
-  <si>
-    <t>Modeling and Model-Driven Engineering</t>
-  </si>
-  <si>
-    <t>Intelligence and automation</t>
-  </si>
-  <si>
-    <t>Adaptability, Interoperability, Dependability</t>
+    <t>Architecture, testing, software re-use</t>
   </si>
   <si>
     <t>Does it contribute to answer RQ1?</t>
   </si>
   <si>
-    <t>Y</t>
+    <t>Maybe partially? The authors mention automotive software ecosystem, and tools, frameworks, approaches, and challenges relate to automotive domain, for me it answer partially, while it focus on automotive domain and list technical and research papers dealing with software ecosystems.
+The authors said: "Several other miscellaneous subjects, such as development and maintenance of automotive reference architecture [P129, P218,
+P35], architecture for supporting federated embedded systems and ecosystems [P90, P276, P88], and architecture for innovative experimental systems [P211, P91], were also discussed in the literature". See also Table A11.</t>
   </si>
   <si>
     <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
   </si>
   <si>
-    <t>Partially</t>
-  </si>
-  <si>
-    <t>Not directly: the authors list advantages to Software Ecosystems (e.g., there exists collaborations), but not present a list of methods, tools, or benefits for Industry/academia collaboration</t>
-  </si>
-  <si>
     <t>Does it contribute to answer RQ2?</t>
   </si>
   <si>
     <t>Application Domain(s) (at least one or domain independent)</t>
   </si>
   <si>
-    <t>Application Domain Independent</t>
+    <t>Automotive</t>
   </si>
   <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
   </si>
   <si>
-    <t>NOTE: Vision Paper</t>
+    <t>The study quality is very high since they follow clear guidelines for systematic studies, but I still think the study is not very valuable for us since there is nothing to do with software eco-systems nor industry academia collaboration</t>
   </si>
   <si>
     <t>RQ1: In the SECO, what are the main challenges faced during the CPS development?</t>
@@ -203,7 +201,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -229,11 +227,6 @@
       <name val="Arial"/>
     </font>
     <font/>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -572,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -601,7 +594,7 @@
     <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="16" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="15" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -614,23 +607,23 @@
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf borderId="20" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
@@ -641,87 +634,84 @@
     <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="22" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="22" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="23" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="23" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="24" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="24" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="24" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1019,7 +1009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="221.25" customHeight="1">
+    <row r="3" ht="229.5" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
@@ -1037,8 +1027,8 @@
       <c r="B4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="17" t="s">
-        <v>7</v>
+      <c r="C4" s="17">
+        <v>0.0</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1046,7 +1036,7 @@
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
       <c r="I4" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -1054,10 +1044,10 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="20" t="s">
         <v>9</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>10</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
@@ -1065,7 +1055,7 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1073,31 +1063,31 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="D6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="E6" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>7</v>
+      <c r="F6" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>13</v>
       </c>
       <c r="I6" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7">
       <c r="A7" s="16">
         <v>5.0</v>
       </c>
@@ -1105,34 +1095,34 @@
         <v>15</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
       <c r="H7" s="18"/>
-      <c r="I7" s="26" t="s">
-        <v>8</v>
+      <c r="I7" s="23" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16">
         <v>6.0</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="26" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
       <c r="H8" s="18"/>
-      <c r="I8" s="23" t="s">
-        <v>19</v>
+      <c r="I8" s="27" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1140,10 +1130,10 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
@@ -1151,7 +1141,7 @@
       <c r="G9" s="25"/>
       <c r="H9" s="18"/>
       <c r="I9" s="21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1159,28 +1149,28 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="27" t="s">
         <v>7</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" s="26" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1188,38 +1178,34 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C11" s="31">
         <f>Quality!C29</f>
-        <v>4.814814815</v>
+        <v>8.888888889</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
-      <c r="I11" s="21" t="s">
-        <v>8</v>
+      <c r="I11" s="32" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="B15" s="33" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="B16" s="33" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="B17" s="33" t="s">
-        <v>26</v>
-      </c>
-    </row>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
     <row r="20" ht="15.75" customHeight="1"/>
@@ -2276,10 +2262,10 @@
     <row r="1">
       <c r="A1" s="34"/>
       <c r="B1" s="35" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D1" s="36"/>
       <c r="E1" s="37"/>
@@ -2287,10 +2273,10 @@
     </row>
     <row r="2">
       <c r="A2" s="39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C2" s="41">
         <v>1.0</v>
@@ -2302,7 +2288,7 @@
     <row r="3">
       <c r="A3" s="43"/>
       <c r="B3" s="40" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C3" s="41">
         <v>1.0</v>
@@ -2314,7 +2300,7 @@
     <row r="4">
       <c r="A4" s="43"/>
       <c r="B4" s="40" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C4" s="41">
         <v>1.0</v>
@@ -2325,7 +2311,7 @@
     <row r="5">
       <c r="A5" s="43"/>
       <c r="B5" s="40" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="41">
         <v>1.0</v>
@@ -2336,70 +2322,70 @@
     <row r="6">
       <c r="A6" s="43"/>
       <c r="B6" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="44">
-        <v>0.5</v>
+        <v>32</v>
+      </c>
+      <c r="C6" s="41">
+        <v>1.0</v>
       </c>
       <c r="D6" s="36"/>
       <c r="E6" s="36"/>
     </row>
     <row r="7">
-      <c r="A7" s="45"/>
+      <c r="A7" s="44"/>
       <c r="B7" s="40" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7" s="41">
         <v>1.0</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="45">
         <f>COUNTIF(B2:B7,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="45">
         <f>(SUM(C2:C7)/D7)*10</f>
-        <v>9.166666667</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="49">
-        <v>0.0</v>
+      <c r="A8" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="48">
+        <v>1.0</v>
       </c>
       <c r="D8" s="36"/>
       <c r="E8" s="36"/>
     </row>
     <row r="9">
       <c r="A9" s="43"/>
-      <c r="B9" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="49">
-        <v>0.0</v>
+      <c r="B9" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="48">
+        <v>1.0</v>
       </c>
       <c r="D9" s="36"/>
       <c r="E9" s="36"/>
     </row>
     <row r="10">
       <c r="A10" s="43"/>
-      <c r="B10" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="49">
-        <v>0.5</v>
+      <c r="B10" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="48">
+        <v>1.0</v>
       </c>
       <c r="D10" s="36"/>
       <c r="E10" s="36"/>
     </row>
     <row r="11">
       <c r="A11" s="43"/>
-      <c r="B11" s="48" t="s">
-        <v>40</v>
+      <c r="B11" s="47" t="s">
+        <v>38</v>
       </c>
       <c r="C11" s="49">
         <v>0.0</v>
@@ -2409,21 +2395,21 @@
     </row>
     <row r="12">
       <c r="A12" s="43"/>
-      <c r="B12" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="49">
-        <v>0.0</v>
+      <c r="B12" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="48">
+        <v>1.0</v>
       </c>
       <c r="D12" s="36"/>
       <c r="E12" s="36"/>
     </row>
     <row r="13">
       <c r="A13" s="43"/>
-      <c r="B13" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="50">
+      <c r="B13" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="48">
         <v>1.0</v>
       </c>
       <c r="D13" s="36"/>
@@ -2431,10 +2417,10 @@
     </row>
     <row r="14">
       <c r="A14" s="43"/>
-      <c r="B14" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="50">
+      <c r="B14" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="48">
         <v>1.0</v>
       </c>
       <c r="D14" s="36"/>
@@ -2442,93 +2428,93 @@
     </row>
     <row r="15">
       <c r="A15" s="43"/>
-      <c r="B15" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="49">
-        <v>0.5</v>
+      <c r="B15" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="48">
+        <v>1.0</v>
       </c>
       <c r="D15" s="36"/>
       <c r="E15" s="36"/>
     </row>
     <row r="16">
       <c r="A16" s="43"/>
-      <c r="B16" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="49">
-        <v>0.0</v>
+      <c r="B16" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="48">
+        <v>1.0</v>
       </c>
       <c r="D16" s="36"/>
       <c r="E16" s="36"/>
     </row>
     <row r="17">
       <c r="A17" s="43"/>
-      <c r="B17" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="49">
-        <v>0.0</v>
+      <c r="B17" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="48">
+        <v>1.0</v>
       </c>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
     </row>
     <row r="18">
       <c r="A18" s="43"/>
-      <c r="B18" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="49">
-        <v>0.0</v>
+      <c r="B18" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="48">
+        <v>1.0</v>
       </c>
       <c r="D18" s="36"/>
       <c r="E18" s="36"/>
     </row>
     <row r="19">
-      <c r="A19" s="45"/>
-      <c r="B19" s="48" t="s">
-        <v>48</v>
+      <c r="A19" s="44"/>
+      <c r="B19" s="47" t="s">
+        <v>46</v>
       </c>
       <c r="C19" s="49">
-        <v>0.0</v>
-      </c>
-      <c r="D19" s="46">
+        <v>0.5</v>
+      </c>
+      <c r="D19" s="45">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
         <v>12</v>
       </c>
-      <c r="E19" s="46">
+      <c r="E19" s="45">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>2.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="52" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="53">
-        <v>0.5</v>
+      <c r="A20" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="52">
+        <v>1.0</v>
       </c>
       <c r="D20" s="36"/>
       <c r="E20" s="36"/>
     </row>
     <row r="21">
       <c r="A21" s="43"/>
-      <c r="B21" s="52" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="53">
-        <v>0.0</v>
+      <c r="B21" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="52">
+        <v>1.0</v>
       </c>
       <c r="D21" s="36"/>
       <c r="E21" s="36"/>
     </row>
     <row r="22">
       <c r="A22" s="43"/>
-      <c r="B22" s="52" t="s">
-        <v>52</v>
+      <c r="B22" s="51" t="s">
+        <v>50</v>
       </c>
       <c r="C22" s="53">
         <v>0.5</v>
@@ -2538,11 +2524,11 @@
     </row>
     <row r="23">
       <c r="A23" s="43"/>
-      <c r="B23" s="52" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="53">
-        <v>0.5</v>
+      <c r="B23" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="52">
+        <v>1.0</v>
       </c>
       <c r="D23" s="37"/>
       <c r="E23" s="37"/>
@@ -2550,42 +2536,42 @@
     </row>
     <row r="24">
       <c r="A24" s="43"/>
-      <c r="B24" s="52" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="53">
-        <v>0.5</v>
+      <c r="B24" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="52">
+        <v>1.0</v>
       </c>
       <c r="D24" s="37"/>
       <c r="E24" s="37"/>
       <c r="F24" s="42"/>
     </row>
     <row r="25">
-      <c r="A25" s="45"/>
-      <c r="B25" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="54">
+      <c r="A25" s="44"/>
+      <c r="B25" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="52">
         <v>1.0</v>
       </c>
-      <c r="D25" s="55">
+      <c r="D25" s="54">
         <f>COUNTIF(B20:B25,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E25" s="55">
+      <c r="E25" s="54">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>5</v>
+        <v>9.166666667</v>
       </c>
       <c r="F25" s="42"/>
     </row>
     <row r="26">
-      <c r="A26" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="57" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="58">
+      <c r="A26" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="57">
         <v>1.0</v>
       </c>
       <c r="D26" s="37"/>
@@ -2594,42 +2580,42 @@
     </row>
     <row r="27">
       <c r="A27" s="43"/>
-      <c r="B27" s="57" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="59">
-        <v>0.5</v>
+      <c r="B27" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="57">
+        <v>1.0</v>
       </c>
       <c r="D27" s="37"/>
       <c r="E27" s="37"/>
       <c r="F27" s="42"/>
     </row>
     <row r="28">
-      <c r="A28" s="45"/>
-      <c r="B28" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="59">
+      <c r="A28" s="44"/>
+      <c r="B28" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="58">
         <v>0.0</v>
       </c>
-      <c r="D28" s="55">
+      <c r="D28" s="54">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
         <v>3</v>
       </c>
-      <c r="E28" s="55">
+      <c r="E28" s="54">
         <f>(SUM(C26:C28)/D28)*10</f>
-        <v>5</v>
+        <v>6.666666667</v>
       </c>
       <c r="F28" s="42"/>
     </row>
     <row r="29">
-      <c r="B29" s="60">
+      <c r="B29" s="59">
         <f>COUNTIF(B2:B28,"&lt;&gt;text")</f>
         <v>27</v>
       </c>
-      <c r="C29" s="60">
+      <c r="C29" s="59">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>4.814814815</v>
+        <v>8.888888889</v>
       </c>
     </row>
   </sheetData>
